--- a/DCU.xlsx
+++ b/DCU.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05CA6065-87EC-4F4D-AAB2-CFDA6154C7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21697" yWindow="-1140" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DCUDATASHEET" sheetId="1" r:id="rId1"/>
